--- a/docs/rebar_anchorage/鉄筋定着問題集.xlsx
+++ b/docs/rebar_anchorage/鉄筋定着問題集.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="目次" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6-1 応力伝達機構" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6-2 定着長の種類" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6-3 L2・L2h 暗記" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6-4 計算仮定条件" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6-5 部材内と仕口内" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="解答" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="目次" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="6-1 応力伝達機構" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="6-2 定着長の種類" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="6-3 L2・L2h 暗記" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="6-4 計算仮定条件" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="6-5 部材内と仕口内" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="解答" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -219,7 +219,7 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>0</col>
@@ -234,13 +234,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -249,7 +249,7 @@
 </file>
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>0</col>
@@ -264,13 +264,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -279,7 +279,7 @@
 </file>
 
 <file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>0</col>
@@ -294,13 +294,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -1021,7 +1021,7 @@
     <row r="42" ht="32" customHeight="1">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>Lb = (σt / (10·fb)) · db。σt=295 N/mm²（SD295 の許容引張、短期）、fb=2.0 N/mm²、db=22mm（D22）のとき Lb を求めよ（mm）。</t>
+          <t>Lb = (σt / (4·fb)) · db（鉄筋の引張力と付着抵抗の釣合いから導かれる）。σt=295 N/mm²（SD295 の許容引張、短期）、fb=2.0 N/mm²、db=22mm（D22）のとき Lb を求めよ（mm）。</t>
         </is>
       </c>
     </row>
@@ -2061,7 +2061,7 @@
     <row r="8" ht="44" customHeight="1">
       <c r="A8" s="9" t="inlineStr">
         <is>
-          <t>問2：Lb = (σt/(10·fb))·db = (295/(10·2.0))·22 = (295/20)·22 = 14.75·22 = 324.5 ≒ 325mm。</t>
+          <t>問2：Lb = (σt/(4·fb))·db = (295/(4×2.0))·22 = 36.9×22 = 811 ≒ 810mm（約37db）。慣用の40dとおおむね対応する。釣合い：T=σt·(π·db²/4) ＝ 付着抵抗 fb·(π·db)·Lb。</t>
         </is>
       </c>
     </row>

--- a/docs/rebar_anchorage/鉄筋定着問題集.xlsx
+++ b/docs/rebar_anchorage/鉄筋定着問題集.xlsx
@@ -241,6 +241,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -271,6 +274,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -279,6 +285,66 @@
 </file>
 
 <file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>31</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="8191500" cy="3524250"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>30</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="8191500" cy="3486150"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
@@ -301,6 +367,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -908,8 +977,8 @@
     <mergeCell ref="A3:H3"/>
     <mergeCell ref="A30:H30"/>
     <mergeCell ref="A46:H46"/>
+    <mergeCell ref="A36:H36"/>
     <mergeCell ref="A33:H33"/>
-    <mergeCell ref="A36:H36"/>
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A37:H37"/>
     <mergeCell ref="A31:H31"/>
@@ -1069,8 +1138,8 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="A50:H50"/>
     <mergeCell ref="A45:H45"/>
-    <mergeCell ref="A50:H50"/>
     <mergeCell ref="A3:H3"/>
     <mergeCell ref="A39:H39"/>
     <mergeCell ref="A42:H42"/>
@@ -1093,7 +1162,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G29"/>
+  <dimension ref="A1:H31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1519,8 +1588,15 @@
         </is>
       </c>
     </row>
+    <row r="31" ht="22" customHeight="1">
+      <c r="A31" s="8" t="inlineStr">
+        <is>
+          <t>■ 補足図（理解の整理）</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A13:G13"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A3:G3"/>
@@ -1530,9 +1606,11 @@
     <mergeCell ref="A15:G15"/>
     <mergeCell ref="A29:G29"/>
     <mergeCell ref="A25:G25"/>
+    <mergeCell ref="A31:H31"/>
     <mergeCell ref="A28:G28"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -1542,7 +1620,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H28"/>
+  <dimension ref="A1:H30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1788,11 +1866,19 @@
         </is>
       </c>
     </row>
+    <row r="30" ht="22" customHeight="1">
+      <c r="A30" s="8" t="inlineStr">
+        <is>
+          <t>■ 補足図（理解の整理）</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A18:H18"/>
     <mergeCell ref="A4:H4"/>
     <mergeCell ref="A3:H3"/>
+    <mergeCell ref="A30:H30"/>
     <mergeCell ref="A15:H15"/>
     <mergeCell ref="A16:H16"/>
     <mergeCell ref="A28:H28"/>
@@ -1802,6 +1888,7 @@
     <mergeCell ref="A27:H27"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
